--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_AMICS CASTELLÓ.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_AMICS CASTELLÓ.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,31 +631,31 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3222</v>
+        <v>3.2058</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7596999999999998</v>
+        <v>1.6433</v>
       </c>
       <c r="F3" t="n">
         <v>1.5625</v>
       </c>
       <c r="G3" t="n">
-        <v>5.888100000000001</v>
+        <v>6.771700000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>8.0297</v>
+        <v>8.3215</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.1414</v>
+        <v>-1.5497</v>
       </c>
       <c r="J3" t="n">
-        <v>9.643000000000001</v>
+        <v>10.5265</v>
       </c>
       <c r="K3" t="n">
-        <v>9.0511</v>
+        <v>9.3429</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5919</v>
+        <v>1.1836</v>
       </c>
       <c r="M3" t="n">
         <v>-3.7549</v>
@@ -697,7 +697,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,76 +706,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0507</v>
+        <v>1.7113</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0507</v>
+        <v>-2.6093</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>4.3207</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0507</v>
+        <v>-4.1339</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4589</v>
+        <v>-0.9251999999999998</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5918</v>
+        <v>-3.2086</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0507</v>
+        <v>-1.4892</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4589</v>
+        <v>-0.1142000000000003</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5918</v>
+        <v>-1.3752</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-2.6446</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.8111999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-1.8336</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.3151</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.4932</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>7.8084</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.05059999999999992</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.8118000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.4794</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.1849</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.7054</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>G. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -787,73 +787,73 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7113</v>
+        <v>1.6013</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.6093</v>
+        <v>3.0897</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3207</v>
+        <v>-1.4885</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.1339</v>
+        <v>-1.5072</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9251999999999998</v>
+        <v>-1.5919</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.2086</v>
+        <v>0.08460000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4892</v>
+        <v>4.2661</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1142000000000003</v>
+        <v>1.7321</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3752</v>
+        <v>2.5341</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6446</v>
+        <v>-5.773400000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8111999999999999</v>
+        <v>-3.324</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8336</v>
+        <v>-2.4494</v>
       </c>
       <c r="P5" t="n">
-        <v>4.3151</v>
+        <v>3.9041</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4932</v>
+        <v>-3.0822</v>
       </c>
       <c r="R5" t="n">
-        <v>7.8084</v>
+        <v>6.9863</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05059999999999992</v>
+        <v>-0.08879999999999993</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8118000000000001</v>
+        <v>0.1386999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8624000000000001</v>
+        <v>-0.2275</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4794</v>
+        <v>-0.7068</v>
       </c>
       <c r="W5" t="n">
-        <v>3.1849</v>
+        <v>1.7671</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7054</v>
+        <v>-2.4739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. IGLESIAS FERNANDEZ</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -865,73 +865,73 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6013</v>
+        <v>0.4010999999999998</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0897</v>
+        <v>-4.2423</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4885</v>
+        <v>4.6434</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5072</v>
+        <v>-4.5204</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5919</v>
+        <v>0.4553000000000003</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08460000000000001</v>
+        <v>-4.9759</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2661</v>
+        <v>-0.3961999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7321</v>
+        <v>0.9778000000000002</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5341</v>
+        <v>-1.3739</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.773400000000001</v>
+        <v>-4.1241</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.324</v>
+        <v>-0.5223</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.4494</v>
+        <v>-3.6018</v>
       </c>
       <c r="P6" t="n">
-        <v>3.9041</v>
+        <v>1.6439</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0822</v>
+        <v>-6.3699</v>
       </c>
       <c r="R6" t="n">
-        <v>6.9863</v>
+        <v>8.0138</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.08879999999999993</v>
+        <v>0.9091</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1386999999999999</v>
+        <v>0.4964</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2275</v>
+        <v>0.4128000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7068</v>
+        <v>2.3685</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7671</v>
+        <v>2.0273</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4739</v>
+        <v>0.3411</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -940,76 +940,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8835999999999999</v>
+        <v>-0.8672000000000004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8835999999999999</v>
+        <v>-6.103</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>5.2359</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8835999999999999</v>
+        <v>-6.2914</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2918</v>
+        <v>-2.259500000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5918</v>
+        <v>-4.0318</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8835999999999999</v>
+        <v>-1.4679</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2918</v>
+        <v>-0.6432999999999995</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5918</v>
+        <v>-0.8244999999999998</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-4.8233</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.6161</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-3.2073</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.4384</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-8.6302</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>10.0687</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.7064</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7966</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.09029999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2795</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1986</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.08089999999999997</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1021,73 +1021,73 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4010999999999998</v>
+        <v>-1.7385</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.2423</v>
+        <v>-6.8034</v>
       </c>
       <c r="F8" t="n">
-        <v>4.6434</v>
+        <v>5.065</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.5204</v>
+        <v>-5.1325</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4553000000000003</v>
+        <v>1.767</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.9759</v>
+        <v>-6.899500000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3961999999999999</v>
+        <v>-2.8511</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9778000000000002</v>
+        <v>2.862</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3739</v>
+        <v>-5.713000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.1241</v>
+        <v>-2.2814</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5223</v>
+        <v>-1.095</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.6018</v>
+        <v>-1.1864</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6439</v>
+        <v>3.4932</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.3699</v>
+        <v>-4.3151</v>
       </c>
       <c r="R8" t="n">
-        <v>8.0138</v>
+        <v>7.8083</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9091</v>
+        <v>0.9364</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4964</v>
+        <v>0.6916</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4128000000000001</v>
+        <v>0.2448</v>
       </c>
       <c r="V8" t="n">
-        <v>2.3685</v>
+        <v>-1.0357</v>
       </c>
       <c r="W8" t="n">
-        <v>2.0273</v>
+        <v>-0.3288</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3411</v>
+        <v>-0.7068</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>D. LOZANO GIMENEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1099,73 +1099,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8672000000000004</v>
+        <v>-3.1485</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.103</v>
+        <v>-1.6556</v>
       </c>
       <c r="F9" t="n">
-        <v>5.2359</v>
+        <v>-1.4928</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.2914</v>
+        <v>-1.8207</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.259500000000001</v>
+        <v>-1</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.0318</v>
+        <v>-0.8208</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4679</v>
+        <v>-0.5528000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6432999999999995</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8244999999999998</v>
+        <v>-0.6306</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.8233</v>
+        <v>-1.2679</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6161</v>
+        <v>-1.0778</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.2073</v>
+        <v>-0.1902</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4384</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-8.6302</v>
+        <v>-1.0274</v>
       </c>
       <c r="R9" t="n">
-        <v>10.0687</v>
+        <v>1.0274</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7064</v>
+        <v>-0.4989</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7966</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09029999999999999</v>
+        <v>-0.4234</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2795</v>
+        <v>-0.8288</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1986</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.08089999999999997</v>
+        <v>-0.8288</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1177,73 +1177,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7385</v>
+        <v>-3.1572</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.8034</v>
+        <v>0.5077999999999996</v>
       </c>
       <c r="F10" t="n">
-        <v>5.065</v>
+        <v>-3.665</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.1325</v>
+        <v>3.1174</v>
       </c>
       <c r="H10" t="n">
-        <v>1.767</v>
+        <v>0.9412</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.899500000000001</v>
+        <v>2.1761</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.8511</v>
+        <v>10.452</v>
       </c>
       <c r="K10" t="n">
-        <v>2.862</v>
+        <v>5.1167</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.713000000000001</v>
+        <v>5.3352</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2814</v>
+        <v>-7.3343</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.095</v>
+        <v>-4.1755</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1864</v>
+        <v>-3.159</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4932</v>
+        <v>-1.4385</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.3151</v>
+        <v>-9.4521</v>
       </c>
       <c r="R10" t="n">
-        <v>7.8083</v>
+        <v>8.0138</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9364</v>
+        <v>-0.7746999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6916</v>
+        <v>-1.0809</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2448</v>
+        <v>0.3062</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0357</v>
+        <v>-4.0616</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3288</v>
+        <v>0.589</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7068</v>
+        <v>-4.6507</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. LOZANO GIMENEZ</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1252,76 +1252,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1485</v>
+        <v>-4.5687</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6556</v>
+        <v>-3.2685</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4928</v>
+        <v>-1.3002</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8207</v>
+        <v>-4.0018</v>
       </c>
       <c r="H11" t="n">
-        <v>-1</v>
+        <v>-2.4408</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8208</v>
+        <v>-1.561</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5528000000000001</v>
+        <v>-2.4763</v>
       </c>
       <c r="K11" t="n">
-        <v>0.07779999999999999</v>
+        <v>-1.1366</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6306</v>
+        <v>-1.3396</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2679</v>
+        <v>-1.5255</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0778</v>
+        <v>-1.3041</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1902</v>
+        <v>-0.2214</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.2055</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.0274</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0274</v>
+        <v>1.2329</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4989</v>
+        <v>-0.2532</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0045</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4234</v>
+        <v>-0.2487</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8288</v>
+        <v>-0.5192</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8288</v>
+        <v>-0.7589</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1333,73 +1333,73 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1572</v>
+        <v>-4.7889</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5077999999999996</v>
+        <v>-3.874</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.665</v>
+        <v>-0.9149</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1174</v>
+        <v>-6.565300000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9412</v>
+        <v>-4.989</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1761</v>
+        <v>-1.5763</v>
       </c>
       <c r="J12" t="n">
-        <v>10.452</v>
+        <v>-3.1185</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1167</v>
+        <v>-2.2548</v>
       </c>
       <c r="L12" t="n">
-        <v>5.3352</v>
+        <v>-0.8639999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.3343</v>
+        <v>-3.4467</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.1755</v>
+        <v>-2.7343</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.159</v>
+        <v>-0.7124000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.4385</v>
+        <v>1.0275</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.4521</v>
+        <v>-2.0548</v>
       </c>
       <c r="R12" t="n">
-        <v>8.0138</v>
+        <v>3.0823</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7746999999999999</v>
+        <v>0.2901</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0809</v>
+        <v>-0.1184</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3062</v>
+        <v>0.4085</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.0616</v>
+        <v>0.4588999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0.589</v>
+        <v>1.4178</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.6507</v>
+        <v>-0.9589</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>R. DIAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1408,76 +1408,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5687</v>
+        <v>-7.3041</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2685</v>
+        <v>-9.608700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3002</v>
+        <v>2.3046</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.0018</v>
+        <v>-3.0232</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4408</v>
+        <v>-1.6583</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.561</v>
+        <v>-1.365</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.4763</v>
+        <v>-1.2214</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1366</v>
+        <v>-1.1053</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3396</v>
+        <v>-0.1159000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5255</v>
+        <v>-1.8018</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3041</v>
+        <v>-0.5529999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2214</v>
+        <v>-1.2488</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2055</v>
+        <v>-3.2877</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0274</v>
+        <v>-8.424700000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2329</v>
+        <v>5.1371</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2532</v>
+        <v>1.5082</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0045</v>
+        <v>0.6059</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2487</v>
+        <v>0.9023</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5192</v>
+        <v>-2.5014</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2397</v>
+        <v>-0.5685</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.7589</v>
+        <v>-1.9328</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1489,222 +1489,66 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.7889</v>
+        <v>-14.6165</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.874</v>
+        <v>-29.8199</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9149</v>
+        <v>15.20360000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.565300000000001</v>
+        <v>-26.6758</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.989</v>
+        <v>-2.550799999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.5763</v>
+        <v>-24.1252</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.1185</v>
+        <v>16.834</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.2548</v>
+        <v>18.8343</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8639999999999999</v>
+        <v>-2.0002</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.4467</v>
+        <v>-43.5091</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.7343</v>
+        <v>-21.3851</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7124000000000001</v>
+        <v>-22.1244</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0275</v>
+        <v>9.246500000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0548</v>
+        <v>-63.69900000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>3.0823</v>
+        <v>72.9462</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2901</v>
+        <v>9.0318</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1184</v>
+        <v>6.169300000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4085</v>
+        <v>2.8628</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4588999999999999</v>
+        <v>-6.219200000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4178</v>
+        <v>10.8763</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.9589</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>R. DIAZ DEL VALLE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>AMICS CASTELLÓ</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-9.3546</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-11.6593</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.3046</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-5.0739</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-3.1172</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-1.9567</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-3.272</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-2.5642</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-0.7077</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-1.8018</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.5529999999999999</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-1.2488</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-3.2877</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-8.424700000000001</v>
-      </c>
-      <c r="R15" t="n">
-        <v>5.1371</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.5082</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.6059</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.9023</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-2.5014</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-0.5685</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.9328</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AMICS CASTELLÓ</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-14.6163</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-29.8198</v>
-      </c>
-      <c r="F16" t="n">
-        <v>15.20360000000001</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-26.6758</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-2.550800000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-24.125</v>
-      </c>
-      <c r="J16" t="n">
-        <v>16.83420000000001</v>
-      </c>
-      <c r="K16" t="n">
-        <v>18.8343</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-2.0001</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-43.5091</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-21.3851</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-22.1244</v>
-      </c>
-      <c r="P16" t="n">
-        <v>9.246500000000001</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-63.69900000000001</v>
-      </c>
-      <c r="R16" t="n">
-        <v>72.9462</v>
-      </c>
-      <c r="S16" t="n">
-        <v>9.0318</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6.169300000000001</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.8628</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-6.219200000000001</v>
-      </c>
-      <c r="W16" t="n">
-        <v>10.8763</v>
-      </c>
-      <c r="X16" t="n">
         <v>-17.0954</v>
       </c>
     </row>
